--- a/macro/양식/키워드변경_양식.xlsx
+++ b/macro/양식/키워드변경_양식.xlsx
@@ -35,7 +35,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +45,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007B1FA2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00059669"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,12 +79,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,17 +464,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Pcode 또는 MID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>키워드</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>메모</t>
         </is>

--- a/macro/양식/키워드변경_양식.xlsx
+++ b/macro/양식/키워드변경_양식.xlsx
@@ -455,12 +455,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -472,11 +471,6 @@
       <c r="B1" s="3" t="inlineStr">
         <is>
           <t>키워드</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>메모</t>
         </is>
       </c>
     </row>
@@ -491,11 +485,6 @@
           <t>강남 맛집,강남 맛집투어</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>예: 키워드 콤마로 여러 개</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/macro/양식/키워드변경_양식.xlsx
+++ b/macro/양식/키워드변경_양식.xlsx
@@ -455,11 +455,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -470,7 +471,12 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>키워드</t>
+          <t>비즈핏 키워드</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>유입플 키워드</t>
         </is>
       </c>
     </row>
@@ -485,6 +491,11 @@
           <t>강남 맛집,강남 맛집투어</t>
         </is>
       </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>강남맛집,강남맛집추천</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/macro/양식/키워드변경_양식.xlsx
+++ b/macro/양식/키워드변경_양식.xlsx
@@ -455,26 +455,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Pcode 또는 MID</t>
+          <t>영업점</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Pcode</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>비즈핏 키워드</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>유입플 키워드</t>
         </is>
@@ -483,15 +495,25 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>1839711962</t>
+          <t>제이솔컴퍼니</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>강남 맛집,강남 맛집투어</t>
+          <t>1230085864</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>P2116A864DC2B0CF2</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>귀금속,귀금속방,귀금속위치</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>강남맛집,강남맛집추천</t>
         </is>
